--- a/excel-files/CALOOCAN/M.B. ASISTIO, SR. HIGH SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/M.B. ASISTIO, SR. HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C08B0756-6578-447F-AD82-6CB3A8FF0FA7}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB05749A-2C9E-4A57-BE7C-B4E06F78B743}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -762,6 +762,10 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -773,10 +777,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3530,11 +3530,11 @@
         <v>7</v>
       </c>
       <c r="I1" s="6"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
       <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" ht="42.75" customHeight="1">
@@ -3556,11 +3556,11 @@
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
     </row>
     <row r="3" spans="1:15" ht="29.25" customHeight="1">
       <c r="A3" s="1">
@@ -3581,11 +3581,11 @@
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1">
       <c r="A4" s="1">
@@ -3606,11 +3606,11 @@
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
     </row>
     <row r="5" spans="1:15" ht="25.5" customHeight="1">
       <c r="A5" s="1">
@@ -3631,11 +3631,11 @@
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
     </row>
     <row r="6" spans="1:15" ht="19.5">
       <c r="A6" s="1">
@@ -3656,21 +3656,21 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
     </row>
     <row r="7" spans="1:15" ht="19.5">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
     </row>
     <row r="8" spans="1:15" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3691,11 +3691,11 @@
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
     </row>
     <row r="9" spans="1:15" ht="29.25" customHeight="1">
       <c r="A9" s="1">
@@ -3716,11 +3716,11 @@
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
     </row>
     <row r="10" spans="1:15" ht="28.5" customHeight="1">
       <c r="A10" s="1">
@@ -3741,11 +3741,11 @@
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
     </row>
     <row r="11" spans="1:15" ht="24" customHeight="1">
       <c r="A11" s="1">
@@ -3766,11 +3766,11 @@
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
     </row>
     <row r="12" spans="1:15" ht="19.5">
       <c r="A12" s="1">
@@ -3791,21 +3791,21 @@
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
     </row>
     <row r="13" spans="1:15" ht="19.5">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
     </row>
     <row r="14" spans="1:15" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -3826,11 +3826,11 @@
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
     </row>
     <row r="15" spans="1:15" ht="29.25" customHeight="1">
       <c r="A15" s="1">
@@ -3851,11 +3851,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
     </row>
     <row r="16" spans="1:15" ht="27" customHeight="1">
       <c r="A16" s="1">
@@ -3876,11 +3876,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
     </row>
     <row r="17" spans="1:14" ht="23.25" customHeight="1">
       <c r="A17" s="1">
@@ -3901,11 +3901,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
     </row>
     <row r="18" spans="1:14" ht="21" customHeight="1">
       <c r="A18" s="1">
@@ -3926,11 +3926,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
     </row>
     <row r="19" spans="1:14" ht="19.5">
       <c r="A19" s="1">
@@ -3951,11 +3951,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
     </row>
     <row r="20" spans="1:14" ht="19.5">
       <c r="A20" s="7"/>
@@ -3966,11 +3966,11 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
     </row>
     <row r="21" spans="1:14" ht="28.5" customHeight="1">
       <c r="A21" s="1">
@@ -3991,11 +3991,11 @@
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
     </row>
     <row r="22" spans="1:14" ht="24" customHeight="1">
       <c r="A22" s="1">
@@ -4016,11 +4016,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
     </row>
     <row r="23" spans="1:14" ht="19.5">
       <c r="A23" s="1">
@@ -4041,11 +4041,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
     </row>
     <row r="24" spans="1:14" ht="27" customHeight="1">
       <c r="A24" s="1">
@@ -4066,11 +4066,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
     </row>
     <row r="25" spans="1:14" ht="33.75" customHeight="1">
       <c r="A25" s="1">
@@ -4091,11 +4091,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
     </row>
     <row r="26" spans="1:14" ht="33.75" customHeight="1">
       <c r="A26" s="1">
@@ -4116,11 +4116,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
     </row>
     <row r="27" spans="1:14" ht="33.75" customHeight="1">
       <c r="A27" s="1">
@@ -4141,11 +4141,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
     </row>
     <row r="28" spans="1:14" ht="27.75" customHeight="1">
       <c r="A28" s="1">
@@ -4166,11 +4166,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
     </row>
     <row r="29" spans="1:14" ht="27.75" customHeight="1">
       <c r="A29" s="1">
@@ -4191,11 +4191,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="42"/>
     </row>
     <row r="30" spans="1:14" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
@@ -4206,11 +4206,11 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="42"/>
     </row>
     <row r="31" spans="1:14" ht="27.75" customHeight="1">
       <c r="A31" s="1">
@@ -4231,11 +4231,11 @@
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="42"/>
     </row>
     <row r="32" spans="1:14" ht="27.75" customHeight="1">
       <c r="A32" s="1">
@@ -4256,11 +4256,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
     </row>
     <row r="33" spans="1:14" ht="27.75" customHeight="1">
       <c r="A33" s="1">
@@ -4281,11 +4281,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
     </row>
     <row r="34" spans="1:14" ht="27.75" customHeight="1">
       <c r="A34" s="1">
@@ -4306,11 +4306,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
     </row>
     <row r="35" spans="1:14" ht="39" customHeight="1">
       <c r="A35" s="1">
@@ -4331,11 +4331,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42"/>
     </row>
     <row r="36" spans="1:14" ht="27.75" customHeight="1">
       <c r="A36" s="1">
@@ -4356,11 +4356,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
     </row>
     <row r="37" spans="1:14" ht="27.75" customHeight="1">
       <c r="A37" s="1">
@@ -4381,11 +4381,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="42"/>
+      <c r="N37" s="42"/>
     </row>
     <row r="38" spans="1:14" ht="27.75" customHeight="1">
       <c r="A38" s="1">
@@ -4406,11 +4406,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="42"/>
+      <c r="N38" s="42"/>
     </row>
     <row r="39" spans="1:14" ht="27.75" customHeight="1">
       <c r="A39" s="1">
@@ -4431,11 +4431,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="42"/>
+      <c r="N39" s="42"/>
     </row>
     <row r="40" spans="1:14" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
@@ -4446,11 +4446,11 @@
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
+      <c r="N40" s="42"/>
     </row>
     <row r="41" spans="1:14" ht="27.75" customHeight="1">
       <c r="A41" s="1">
@@ -4471,11 +4471,11 @@
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="46"/>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="42"/>
+      <c r="N41" s="42"/>
     </row>
     <row r="42" spans="1:14" ht="27.75" customHeight="1">
       <c r="A42" s="1">
@@ -4496,11 +4496,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
     </row>
     <row r="43" spans="1:14" ht="27.75" customHeight="1">
       <c r="A43" s="1">
@@ -4521,11 +4521,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="42"/>
     </row>
     <row r="44" spans="1:14" ht="27.75" customHeight="1">
       <c r="A44" s="1">
@@ -4546,11 +4546,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="42"/>
+      <c r="N44" s="42"/>
     </row>
     <row r="45" spans="1:14" ht="36.75" customHeight="1">
       <c r="A45" s="1">
@@ -4571,11 +4571,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="42"/>
+      <c r="N45" s="42"/>
     </row>
     <row r="46" spans="1:14" ht="27.75" customHeight="1">
       <c r="A46" s="1">
@@ -4596,11 +4596,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="42"/>
+      <c r="N46" s="42"/>
     </row>
     <row r="47" spans="1:14" ht="27.75" customHeight="1">
       <c r="A47" s="1">
@@ -4621,11 +4621,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="42"/>
+      <c r="N47" s="42"/>
     </row>
     <row r="48" spans="1:14" ht="27.75" customHeight="1">
       <c r="A48" s="1">
@@ -4646,11 +4646,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
+      <c r="L48" s="42"/>
+      <c r="M48" s="42"/>
+      <c r="N48" s="42"/>
     </row>
     <row r="49" spans="1:14" ht="27.75" customHeight="1">
       <c r="A49" s="1">
@@ -4671,11 +4671,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="42"/>
+      <c r="N49" s="42"/>
     </row>
     <row r="50" spans="1:14" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
@@ -4686,11 +4686,11 @@
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
+      <c r="L50" s="42"/>
+      <c r="M50" s="42"/>
+      <c r="N50" s="42"/>
     </row>
     <row r="51" spans="1:14" ht="27.75" customHeight="1">
       <c r="A51" s="10">
@@ -4717,11 +4717,11 @@
         <f t="shared" ref="H51:H59" si="11">IF((D51-C51)&lt;0,0,D51-C51)</f>
         <v>924</v>
       </c>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42"/>
+      <c r="M51" s="42"/>
+      <c r="N51" s="42"/>
     </row>
     <row r="52" spans="1:14" ht="27.75" customHeight="1">
       <c r="A52" s="10">
@@ -4744,11 +4744,11 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
+      <c r="L52" s="42"/>
+      <c r="M52" s="42"/>
+      <c r="N52" s="42"/>
     </row>
     <row r="53" spans="1:14" ht="27.75" customHeight="1">
       <c r="A53" s="10">
@@ -4775,11 +4775,11 @@
         <f t="shared" si="11"/>
         <v>924</v>
       </c>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="46"/>
-      <c r="M53" s="46"/>
-      <c r="N53" s="46"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="42"/>
+      <c r="M53" s="42"/>
+      <c r="N53" s="42"/>
     </row>
     <row r="54" spans="1:14" ht="27.75" customHeight="1">
       <c r="A54" s="10">
@@ -4802,11 +4802,11 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="42"/>
+      <c r="N54" s="42"/>
     </row>
     <row r="55" spans="1:14" ht="39" customHeight="1">
       <c r="A55" s="10">
@@ -4833,11 +4833,11 @@
         <f t="shared" si="11"/>
         <v>924</v>
       </c>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
-      <c r="M55" s="46"/>
-      <c r="N55" s="46"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="42"/>
+      <c r="N55" s="42"/>
     </row>
     <row r="56" spans="1:14" ht="27.75" customHeight="1">
       <c r="A56" s="10">
@@ -4864,11 +4864,11 @@
         <f t="shared" si="11"/>
         <v>924</v>
       </c>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
-      <c r="M56" s="46"/>
-      <c r="N56" s="46"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
+      <c r="L56" s="42"/>
+      <c r="M56" s="42"/>
+      <c r="N56" s="42"/>
     </row>
     <row r="57" spans="1:14" ht="27.75" customHeight="1">
       <c r="A57" s="10">
@@ -4895,11 +4895,11 @@
         <f t="shared" si="11"/>
         <v>924</v>
       </c>
-      <c r="J57" s="46"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="46"/>
-      <c r="M57" s="46"/>
-      <c r="N57" s="46"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
+      <c r="L57" s="42"/>
+      <c r="M57" s="42"/>
+      <c r="N57" s="42"/>
     </row>
     <row r="58" spans="1:14" ht="27.75" customHeight="1">
       <c r="A58" s="10">
@@ -4926,11 +4926,11 @@
         <f t="shared" si="11"/>
         <v>924</v>
       </c>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="46"/>
-      <c r="M58" s="46"/>
-      <c r="N58" s="46"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
+      <c r="L58" s="42"/>
+      <c r="M58" s="42"/>
+      <c r="N58" s="42"/>
     </row>
     <row r="59" spans="1:14" ht="27.75" customHeight="1">
       <c r="A59" s="10">
@@ -4957,11 +4957,11 @@
         <f t="shared" si="11"/>
         <v>924</v>
       </c>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-      <c r="L59" s="46"/>
-      <c r="M59" s="46"/>
-      <c r="N59" s="46"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
+      <c r="L59" s="42"/>
+      <c r="M59" s="42"/>
+      <c r="N59" s="42"/>
     </row>
     <row r="60" spans="1:14" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
@@ -4972,11 +4972,11 @@
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-      <c r="M60" s="46"/>
-      <c r="N60" s="46"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
+      <c r="L60" s="42"/>
+      <c r="M60" s="42"/>
+      <c r="N60" s="42"/>
     </row>
     <row r="61" spans="1:14" ht="27.75" customHeight="1">
       <c r="A61" s="10">
@@ -4999,11 +4999,11 @@
         <f t="shared" ref="H61:H69" si="13">IF((D61-C61)&lt;0,0,D61-C61)</f>
         <v>0</v>
       </c>
-      <c r="J61" s="46"/>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
-      <c r="M61" s="46"/>
-      <c r="N61" s="46"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
+      <c r="L61" s="42"/>
+      <c r="M61" s="42"/>
+      <c r="N61" s="42"/>
     </row>
     <row r="62" spans="1:14" ht="27.75" customHeight="1">
       <c r="A62" s="10">
@@ -5026,11 +5026,11 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
-      <c r="L62" s="46"/>
-      <c r="M62" s="46"/>
-      <c r="N62" s="46"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="L62" s="42"/>
+      <c r="M62" s="42"/>
+      <c r="N62" s="42"/>
     </row>
     <row r="63" spans="1:14" ht="27.75" customHeight="1">
       <c r="A63" s="10">
@@ -5057,11 +5057,11 @@
         <f t="shared" si="13"/>
         <v>738</v>
       </c>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
-      <c r="L63" s="46"/>
-      <c r="M63" s="46"/>
-      <c r="N63" s="46"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
+      <c r="L63" s="42"/>
+      <c r="M63" s="42"/>
+      <c r="N63" s="42"/>
     </row>
     <row r="64" spans="1:14" ht="27.75" customHeight="1">
       <c r="A64" s="10">
@@ -5088,11 +5088,11 @@
         <f t="shared" si="13"/>
         <v>738</v>
       </c>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
-      <c r="M64" s="46"/>
-      <c r="N64" s="46"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
+      <c r="L64" s="42"/>
+      <c r="M64" s="42"/>
+      <c r="N64" s="42"/>
     </row>
     <row r="65" spans="1:14" ht="27.75" customHeight="1">
       <c r="A65" s="10">
@@ -5115,11 +5115,11 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J65" s="46"/>
-      <c r="K65" s="46"/>
-      <c r="L65" s="46"/>
-      <c r="M65" s="46"/>
-      <c r="N65" s="46"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
+      <c r="L65" s="42"/>
+      <c r="M65" s="42"/>
+      <c r="N65" s="42"/>
     </row>
     <row r="66" spans="1:14" ht="27.75" customHeight="1">
       <c r="A66" s="10">
@@ -5142,11 +5142,11 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-      <c r="L66" s="46"/>
-      <c r="M66" s="46"/>
-      <c r="N66" s="46"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
+      <c r="L66" s="42"/>
+      <c r="M66" s="42"/>
+      <c r="N66" s="42"/>
     </row>
     <row r="67" spans="1:14" ht="27.75" customHeight="1">
       <c r="A67" s="10">
@@ -5169,11 +5169,11 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-      <c r="L67" s="46"/>
-      <c r="M67" s="46"/>
-      <c r="N67" s="46"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
+      <c r="L67" s="42"/>
+      <c r="M67" s="42"/>
+      <c r="N67" s="42"/>
     </row>
     <row r="68" spans="1:14" ht="27.75" customHeight="1">
       <c r="A68" s="10">
@@ -5196,11 +5196,11 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
-      <c r="L68" s="46"/>
-      <c r="M68" s="46"/>
-      <c r="N68" s="46"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
+      <c r="L68" s="42"/>
+      <c r="M68" s="42"/>
+      <c r="N68" s="42"/>
     </row>
     <row r="69" spans="1:14" ht="27.75" customHeight="1">
       <c r="A69" s="10">
@@ -5223,11 +5223,11 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
-      <c r="L69" s="46"/>
-      <c r="M69" s="46"/>
-      <c r="N69" s="46"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
+      <c r="L69" s="42"/>
+      <c r="M69" s="42"/>
+      <c r="N69" s="42"/>
     </row>
     <row r="70" spans="1:14" ht="27.75" customHeight="1">
       <c r="A70" s="7"/>
@@ -5238,11 +5238,11 @@
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="46"/>
-      <c r="M70" s="46"/>
-      <c r="N70" s="46"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="L70" s="42"/>
+      <c r="M70" s="42"/>
+      <c r="N70" s="42"/>
     </row>
     <row r="71" spans="1:14" ht="27.75" customHeight="1">
       <c r="A71" s="10">
@@ -5265,11 +5265,11 @@
         <f t="shared" ref="H71:H79" si="15">IF((D71-C71)&lt;0,0,D71-C71)</f>
         <v>0</v>
       </c>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="46"/>
-      <c r="M71" s="46"/>
-      <c r="N71" s="46"/>
+      <c r="J71" s="42"/>
+      <c r="K71" s="42"/>
+      <c r="L71" s="42"/>
+      <c r="M71" s="42"/>
+      <c r="N71" s="42"/>
     </row>
     <row r="72" spans="1:14" ht="27.75" customHeight="1">
       <c r="A72" s="10">
@@ -5292,11 +5292,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
-      <c r="L72" s="46"/>
-      <c r="M72" s="46"/>
-      <c r="N72" s="46"/>
+      <c r="J72" s="42"/>
+      <c r="K72" s="42"/>
+      <c r="L72" s="42"/>
+      <c r="M72" s="42"/>
+      <c r="N72" s="42"/>
     </row>
     <row r="73" spans="1:14" ht="27.75" customHeight="1">
       <c r="A73" s="10">
@@ -5319,11 +5319,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
-      <c r="L73" s="46"/>
-      <c r="M73" s="46"/>
-      <c r="N73" s="46"/>
+      <c r="J73" s="42"/>
+      <c r="K73" s="42"/>
+      <c r="L73" s="42"/>
+      <c r="M73" s="42"/>
+      <c r="N73" s="42"/>
     </row>
     <row r="74" spans="1:14" ht="27.75" customHeight="1">
       <c r="A74" s="10">
@@ -5346,11 +5346,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
-      <c r="L74" s="46"/>
-      <c r="M74" s="46"/>
-      <c r="N74" s="46"/>
+      <c r="J74" s="42"/>
+      <c r="K74" s="42"/>
+      <c r="L74" s="42"/>
+      <c r="M74" s="42"/>
+      <c r="N74" s="42"/>
     </row>
     <row r="75" spans="1:14" ht="27.75" customHeight="1">
       <c r="A75" s="10">
@@ -5373,11 +5373,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="46"/>
-      <c r="M75" s="46"/>
-      <c r="N75" s="46"/>
+      <c r="J75" s="42"/>
+      <c r="K75" s="42"/>
+      <c r="L75" s="42"/>
+      <c r="M75" s="42"/>
+      <c r="N75" s="42"/>
     </row>
     <row r="76" spans="1:14" ht="27.75" customHeight="1">
       <c r="A76" s="10">
@@ -5400,11 +5400,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
-      <c r="L76" s="46"/>
-      <c r="M76" s="46"/>
-      <c r="N76" s="46"/>
+      <c r="J76" s="42"/>
+      <c r="K76" s="42"/>
+      <c r="L76" s="42"/>
+      <c r="M76" s="42"/>
+      <c r="N76" s="42"/>
     </row>
     <row r="77" spans="1:14" ht="27.75" customHeight="1">
       <c r="A77" s="10">
@@ -5427,11 +5427,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
-      <c r="L77" s="46"/>
-      <c r="M77" s="46"/>
-      <c r="N77" s="46"/>
+      <c r="J77" s="42"/>
+      <c r="K77" s="42"/>
+      <c r="L77" s="42"/>
+      <c r="M77" s="42"/>
+      <c r="N77" s="42"/>
     </row>
     <row r="78" spans="1:14" ht="27.75" customHeight="1">
       <c r="A78" s="10">
@@ -5454,11 +5454,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
-      <c r="L78" s="46"/>
-      <c r="M78" s="46"/>
-      <c r="N78" s="46"/>
+      <c r="J78" s="42"/>
+      <c r="K78" s="42"/>
+      <c r="L78" s="42"/>
+      <c r="M78" s="42"/>
+      <c r="N78" s="42"/>
     </row>
     <row r="79" spans="1:14" ht="27.75" customHeight="1">
       <c r="A79" s="10">
@@ -5481,11 +5481,11 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
-      <c r="M79" s="46"/>
-      <c r="N79" s="46"/>
+      <c r="J79" s="42"/>
+      <c r="K79" s="42"/>
+      <c r="L79" s="42"/>
+      <c r="M79" s="42"/>
+      <c r="N79" s="42"/>
     </row>
     <row r="80" spans="1:14" ht="27.75" customHeight="1">
       <c r="A80" s="7"/>
@@ -5496,11 +5496,11 @@
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
-      <c r="L80" s="46"/>
-      <c r="M80" s="46"/>
-      <c r="N80" s="46"/>
+      <c r="J80" s="42"/>
+      <c r="K80" s="42"/>
+      <c r="L80" s="42"/>
+      <c r="M80" s="42"/>
+      <c r="N80" s="42"/>
     </row>
     <row r="81" spans="1:14" ht="27.75" customHeight="1">
       <c r="A81" s="10">
@@ -5523,11 +5523,11 @@
         <f t="shared" ref="H81:H89" si="17">IF((D81-C81)&lt;0,0,D81-C81)</f>
         <v>0</v>
       </c>
-      <c r="J81" s="46"/>
-      <c r="K81" s="46"/>
-      <c r="L81" s="46"/>
-      <c r="M81" s="46"/>
-      <c r="N81" s="46"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="42"/>
+      <c r="L81" s="42"/>
+      <c r="M81" s="42"/>
+      <c r="N81" s="42"/>
     </row>
     <row r="82" spans="1:14" ht="27.75" customHeight="1">
       <c r="A82" s="10">
@@ -5550,11 +5550,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J82" s="46"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="46"/>
-      <c r="M82" s="46"/>
-      <c r="N82" s="46"/>
+      <c r="J82" s="42"/>
+      <c r="K82" s="42"/>
+      <c r="L82" s="42"/>
+      <c r="M82" s="42"/>
+      <c r="N82" s="42"/>
     </row>
     <row r="83" spans="1:14" ht="27.75" customHeight="1">
       <c r="A83" s="10">
@@ -5577,11 +5577,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
-      <c r="M83" s="46"/>
-      <c r="N83" s="46"/>
+      <c r="J83" s="42"/>
+      <c r="K83" s="42"/>
+      <c r="L83" s="42"/>
+      <c r="M83" s="42"/>
+      <c r="N83" s="42"/>
     </row>
     <row r="84" spans="1:14" ht="27.75" customHeight="1">
       <c r="A84" s="10">
@@ -5604,11 +5604,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J84" s="46"/>
-      <c r="K84" s="46"/>
-      <c r="L84" s="46"/>
-      <c r="M84" s="46"/>
-      <c r="N84" s="46"/>
+      <c r="J84" s="42"/>
+      <c r="K84" s="42"/>
+      <c r="L84" s="42"/>
+      <c r="M84" s="42"/>
+      <c r="N84" s="42"/>
     </row>
     <row r="85" spans="1:14" ht="27.75" customHeight="1">
       <c r="A85" s="10">
@@ -5631,11 +5631,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J85" s="46"/>
-      <c r="K85" s="46"/>
-      <c r="L85" s="46"/>
-      <c r="M85" s="46"/>
-      <c r="N85" s="46"/>
+      <c r="J85" s="42"/>
+      <c r="K85" s="42"/>
+      <c r="L85" s="42"/>
+      <c r="M85" s="42"/>
+      <c r="N85" s="42"/>
     </row>
     <row r="86" spans="1:14" ht="27.75" customHeight="1">
       <c r="A86" s="10">
@@ -5658,11 +5658,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J86" s="46"/>
-      <c r="K86" s="46"/>
-      <c r="L86" s="46"/>
-      <c r="M86" s="46"/>
-      <c r="N86" s="46"/>
+      <c r="J86" s="42"/>
+      <c r="K86" s="42"/>
+      <c r="L86" s="42"/>
+      <c r="M86" s="42"/>
+      <c r="N86" s="42"/>
     </row>
     <row r="87" spans="1:14" ht="27.75" customHeight="1">
       <c r="A87" s="10">
@@ -5685,11 +5685,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-      <c r="L87" s="46"/>
-      <c r="M87" s="46"/>
-      <c r="N87" s="46"/>
+      <c r="J87" s="42"/>
+      <c r="K87" s="42"/>
+      <c r="L87" s="42"/>
+      <c r="M87" s="42"/>
+      <c r="N87" s="42"/>
     </row>
     <row r="88" spans="1:14" ht="27.75" customHeight="1">
       <c r="A88" s="10">
@@ -5712,11 +5712,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J88" s="46"/>
-      <c r="K88" s="46"/>
-      <c r="L88" s="46"/>
-      <c r="M88" s="46"/>
-      <c r="N88" s="46"/>
+      <c r="J88" s="42"/>
+      <c r="K88" s="42"/>
+      <c r="L88" s="42"/>
+      <c r="M88" s="42"/>
+      <c r="N88" s="42"/>
     </row>
     <row r="89" spans="1:14" ht="27.75" customHeight="1">
       <c r="A89" s="10">
@@ -5739,11 +5739,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J89" s="46"/>
-      <c r="K89" s="46"/>
-      <c r="L89" s="46"/>
-      <c r="M89" s="46"/>
-      <c r="N89" s="46"/>
+      <c r="J89" s="42"/>
+      <c r="K89" s="42"/>
+      <c r="L89" s="42"/>
+      <c r="M89" s="42"/>
+      <c r="N89" s="42"/>
     </row>
     <row r="90" spans="1:14" ht="27.75" customHeight="1">
       <c r="A90" s="7"/>
@@ -5754,11 +5754,11 @@
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
-      <c r="J90" s="46"/>
-      <c r="K90" s="46"/>
-      <c r="L90" s="46"/>
-      <c r="M90" s="46"/>
-      <c r="N90" s="46"/>
+      <c r="J90" s="42"/>
+      <c r="K90" s="42"/>
+      <c r="L90" s="42"/>
+      <c r="M90" s="42"/>
+      <c r="N90" s="42"/>
     </row>
     <row r="91" spans="1:14" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
@@ -5785,11 +5785,11 @@
         <f t="shared" ref="H91:H97" si="19">IF((D91-C91)&lt;0,0,D91-C91)</f>
         <v>130</v>
       </c>
-      <c r="J91" s="46"/>
-      <c r="K91" s="46"/>
-      <c r="L91" s="46"/>
-      <c r="M91" s="46"/>
-      <c r="N91" s="46"/>
+      <c r="J91" s="42"/>
+      <c r="K91" s="42"/>
+      <c r="L91" s="42"/>
+      <c r="M91" s="42"/>
+      <c r="N91" s="42"/>
     </row>
     <row r="92" spans="1:14" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
@@ -5812,11 +5812,11 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J92" s="46"/>
-      <c r="K92" s="46"/>
-      <c r="L92" s="46"/>
-      <c r="M92" s="46"/>
-      <c r="N92" s="46"/>
+      <c r="J92" s="42"/>
+      <c r="K92" s="42"/>
+      <c r="L92" s="42"/>
+      <c r="M92" s="42"/>
+      <c r="N92" s="42"/>
     </row>
     <row r="93" spans="1:14" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
@@ -5843,11 +5843,11 @@
         <f t="shared" si="19"/>
         <v>130</v>
       </c>
-      <c r="J93" s="46"/>
-      <c r="K93" s="46"/>
-      <c r="L93" s="46"/>
-      <c r="M93" s="46"/>
-      <c r="N93" s="46"/>
+      <c r="J93" s="42"/>
+      <c r="K93" s="42"/>
+      <c r="L93" s="42"/>
+      <c r="M93" s="42"/>
+      <c r="N93" s="42"/>
     </row>
     <row r="94" spans="1:14" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
@@ -5874,11 +5874,11 @@
         <f t="shared" si="19"/>
         <v>130</v>
       </c>
-      <c r="J94" s="46"/>
-      <c r="K94" s="46"/>
-      <c r="L94" s="46"/>
-      <c r="M94" s="46"/>
-      <c r="N94" s="46"/>
+      <c r="J94" s="42"/>
+      <c r="K94" s="42"/>
+      <c r="L94" s="42"/>
+      <c r="M94" s="42"/>
+      <c r="N94" s="42"/>
     </row>
     <row r="95" spans="1:14" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
@@ -5905,11 +5905,11 @@
         <f t="shared" si="19"/>
         <v>130</v>
       </c>
-      <c r="J95" s="46"/>
-      <c r="K95" s="46"/>
-      <c r="L95" s="46"/>
-      <c r="M95" s="46"/>
-      <c r="N95" s="46"/>
+      <c r="J95" s="42"/>
+      <c r="K95" s="42"/>
+      <c r="L95" s="42"/>
+      <c r="M95" s="42"/>
+      <c r="N95" s="42"/>
     </row>
     <row r="96" spans="1:14" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
@@ -5936,11 +5936,11 @@
         <f t="shared" si="19"/>
         <v>130</v>
       </c>
-      <c r="J96" s="46"/>
-      <c r="K96" s="46"/>
-      <c r="L96" s="46"/>
-      <c r="M96" s="46"/>
-      <c r="N96" s="46"/>
+      <c r="J96" s="42"/>
+      <c r="K96" s="42"/>
+      <c r="L96" s="42"/>
+      <c r="M96" s="42"/>
+      <c r="N96" s="42"/>
     </row>
     <row r="97" spans="1:14" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
@@ -5967,11 +5967,11 @@
         <f t="shared" si="19"/>
         <v>130</v>
       </c>
-      <c r="J97" s="46"/>
-      <c r="K97" s="46"/>
-      <c r="L97" s="46"/>
-      <c r="M97" s="46"/>
-      <c r="N97" s="46"/>
+      <c r="J97" s="42"/>
+      <c r="K97" s="42"/>
+      <c r="L97" s="42"/>
+      <c r="M97" s="42"/>
+      <c r="N97" s="42"/>
     </row>
     <row r="98" spans="1:14" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
@@ -5998,11 +5998,11 @@
         <f>IF((D98-C98)&lt;0,0,D98-C98)</f>
         <v>130</v>
       </c>
-      <c r="J98" s="46"/>
-      <c r="K98" s="46"/>
-      <c r="L98" s="46"/>
-      <c r="M98" s="46"/>
-      <c r="N98" s="46"/>
+      <c r="J98" s="42"/>
+      <c r="K98" s="42"/>
+      <c r="L98" s="42"/>
+      <c r="M98" s="42"/>
+      <c r="N98" s="42"/>
     </row>
     <row r="99" spans="1:14" ht="38.25">
       <c r="A99" s="1" t="s">
@@ -6065,8 +6065,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E100" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E100 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F100" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -6081,7 +6081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -6111,38 +6111,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14069,186 +14069,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
@@ -14262,15 +14082,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L24:L31 L14:L21 L5:L12 L23 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{2AAD2C34-79D0-4D53-B3BF-FB1FDF16306F}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14285,7 +14108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14315,38 +14138,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -21967,7 +21790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -22547,186 +22370,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22740,12 +22383,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10" xr:uid="{00E2C42B-6A73-40A5-B7BA-69A8F5526F53}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
